--- a/Game_Data.xlsx
+++ b/Game_Data.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Party Profiles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variants" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,12 +483,9 @@
           <t>PC</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -505,12 +503,9 @@
           <t>PC</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -528,12 +523,9 @@
           <t>PC</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -551,12 +543,9 @@
           <t>PC</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -574,12 +563,138 @@
           <t>PC</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Variant ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Base Source</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Max HP</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Init Mod</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Attacks/Round</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>To-Hit</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Resistances</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Immunities</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bad ass</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>billy</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>x2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>+8</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Game_Data.xlsx
+++ b/Game_Data.xlsx
@@ -2,29 +2,33 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15120" yWindow="1930" windowWidth="19590" windowHeight="14420" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Party Profiles" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variants" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -50,12 +54,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -418,154 +423,202 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A1" s="2" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Profile ID</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Character Name</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Default AC</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Default Max HP</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Initiative Modifier</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>PARTY-MAIN</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>PC</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>PARTY-MAIN</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Prag</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>PC</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>PARTY-MAIN</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Roquist</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>PC</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>PARTY-MAIN</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Giggles</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>PC</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>PARTY-MAIN</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Shaddow</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>PC</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
         <v>0</v>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -578,123 +631,211 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K89"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A1" s="2" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>Variant ID</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Base Source</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>Max HP</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Init Mod</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Attacks/Round</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>To-Hit</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>Resistances</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>Immunities</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>bad ass</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>billy</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>x2</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>x1.0</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>nerfed</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>x0.6</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>veterian</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>veterian</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>+8</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>fire</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>x1.35</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>x1.0</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>x1.75</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>x1.5</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>+@</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
